--- a/outputs/Hasil_Analisis_PM25_Surakarta.xlsx
+++ b/outputs/Hasil_Analisis_PM25_Surakarta.xlsx
@@ -18,15 +18,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grid_SARIMA" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grid_Fourier" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SARIMA_D1" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameter_ES" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Akar_Model" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koefisien_Final" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diagnostik_Final" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peramalan" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Uji_DM" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bulanan_Konteks" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rasio_PM" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catatan" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kandidat_MA" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameter_ES" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Akar_Model" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diagnostik_Model" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koefisien_Final" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diagnostik_Final" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peramalan" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Uji_DM" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bulanan_Konteks" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rasio_PM" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catatan" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1186,12 +1188,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1202,454 +1209,122 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Parameter</t>
+          <t>q</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>Nilai</t>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>AIC</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>AICc</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>BIC</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>LB20_p</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SES</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>smoothing_level</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>0.3363348699386235</v>
+          <t>MA(3) galat</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>689.3867562069802</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>690.0250540793206</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>702.4126071369207</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>0.3284973447144561</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SES</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>smoothing_trend</t>
-        </is>
+          <t>MA(2) galat</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>702.3057838397941</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>702.7224505064607</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>712.7662659071592</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>0.04872137034455758</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SES</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>smoothing_seasonal</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SES</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>damping_trend</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SES</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>initial_level</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>22.72355299644492</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SES</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>initial_trend</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SES</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>initial_seasons</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>vektor kosong</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SES</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>use_boxcox</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SES</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>lamda</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>tidak diestimasi</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SES</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>remove_bias</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Holt</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>smoothing_level</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>0.3366581644549069</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Holt</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>smoothing_trend</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Holt</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>smoothing_seasonal</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Holt</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>damping_trend</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Holt</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>initial_level</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>22.81277281377454</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Holt</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>initial_trend</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>-0.02965062182766299</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Holt</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>initial_seasons</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>vektor kosong</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Holt</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>use_boxcox</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Holt</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>lamda</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>tidak diestimasi</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Holt</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>remove_bias</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Holt-Winters</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>smoothing_level</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>1.490116119384766e-08</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Holt-Winters</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>smoothing_trend</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Holt-Winters</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>smoothing_seasonal</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Holt-Winters</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>damping_trend</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Holt-Winters</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>initial_level</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>26.7603918979689</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Holt-Winters</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>initial_trend</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>-0.04122118893408561</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Holt-Winters</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>initial_seasons</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>vektor 52 nilai; awal=-4.1601</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Holt-Winters</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>use_boxcox</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Holt-Winters</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>lamda</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>tidak diestimasi</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Holt-Winters</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>remove_bias</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
+          <t>MA(1) galat</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>707.6506452505778</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>707.8955432097614</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>715.5255636904305</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0.009182463268290147</v>
       </c>
     </row>
   </sheetData>
@@ -1663,7 +1338,484 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Nilai</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>smoothing_level</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>0.3363348699386235</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>smoothing_trend</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>smoothing_seasonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>damping_trend</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>initial_level</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>22.72355299644492</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>initial_trend</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>initial_seasons</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>vektor kosong</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>use_boxcox</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>lamda</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>tidak diestimasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>remove_bias</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Holt</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>smoothing_level</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>0.3366581644549069</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Holt</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>smoothing_trend</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Holt</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>smoothing_seasonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Holt</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>damping_trend</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Holt</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>initial_level</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>22.81277281377454</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Holt</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>initial_trend</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>-0.02965062182766299</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Holt</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>initial_seasons</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>vektor kosong</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Holt</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>use_boxcox</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Holt</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>lamda</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>tidak diestimasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Holt</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>remove_bias</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Holt-Winters</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>smoothing_level</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>1.490116119384766e-08</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Holt-Winters</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>smoothing_trend</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Holt-Winters</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>smoothing_seasonal</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Holt-Winters</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>damping_trend</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Holt-Winters</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>initial_level</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>26.7603918979689</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Holt-Winters</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>initial_trend</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>-0.04122118893408561</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Holt-Winters</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>initial_seasons</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>vektor 52 nilai; awal=-4.1601</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Holt-Winters</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>use_boxcox</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Holt-Winters</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>lamda</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>tidak diestimasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Holt-Winters</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>remove_bias</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1787,24 +1939,102 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>MA(1) galat</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>2.147229554091271</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>2.147229554091271</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stabil (di luar lingkaran satuan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MA(2) galat</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>2.822824945103344</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>2.822824945103344</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stabil (di luar lingkaran satuan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MA(3) galat</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1.264851210581542</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>1.652529905408139</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stabil (di luar lingkaran satuan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>SARIMA(2,1,0)(1,0,0)[52]</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C8" t="n">
         <v>54</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D8" s="4" t="n">
         <v>1.044165737527092</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E8" s="4" t="n">
         <v>2.410988693804381</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Stabil (di luar lingkaran satuan)</t>
         </is>
@@ -1815,7 +2045,342 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>LB10_p</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>LB20_p</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>LB52_p</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>JB_p</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>ARCH_p</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>104</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>0.6461907629394373</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0.5340752650595835</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.6315894122565927</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>0.7336950855120253</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0.01500275037012941</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Holt</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>104</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>0.6452397547039546</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>0.5344432758569706</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.6322189494143795</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0.7344535586706797</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0.01478644176353664</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Holt-Winters</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>104</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>0.05506648067275711</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>0.005944823224896603</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>2.46445056730153e-08</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0.3306380807599507</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0.0036924308809073</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AR(12)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>92</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>0.9993526458943721</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0.9935984804513631</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0.9844828663574842</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0.3126280770014158</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0.03997262192501991</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ARMA(2,3)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>104</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>0.9885478298932324</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0.8634189972435953</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0.8017417665714244</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0.1037993147459295</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0.04531957182070187</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MA(1) galat</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>104</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>0.01680341195436293</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0.009182463268290147</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0.003515958240229792</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0.008289325423495366</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0.0007091031263832435</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MA(2) galat</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>104</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0.08198501902352087</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0.04872137034455758</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0.01372135821018672</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0.01074801161725206</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0.00421109031695578</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MA(3) galat</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>104</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>0.5404391650710407</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0.3284973447144561</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0.1150168272852439</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0.02131983772859065</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0.005025470579332963</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ARIMA(1,1,3)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>104</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>0.9913020802548628</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0.8711266890833191</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0.8397856598545407</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0.4422830927500294</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0.3248577198636435</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SARIMA(2,1,0)(1,0,0)[52]</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>104</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>0.3844637154793804</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0.08110861057741714</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0.1714031800591438</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0.2932440499803436</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0.03959184140104022</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Fourier K=2 + ARIMA(1,1,1)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>104</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>0.6792013675085168</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0.5335656739696019</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0.5104487035237933</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0.0005363247549151988</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0.3682238651774094</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1975,7 +2540,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2140,7 +2705,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2434,7 +2999,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2674,7 +3239,1673 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D117"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>week_start</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>pm25</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>n_hours</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>44781</v>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>23.20297619047619</v>
+      </c>
+      <c r="C2" t="n">
+        <v>168</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>44788</v>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>25.58095238095238</v>
+      </c>
+      <c r="C3" t="n">
+        <v>168</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>44795</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>17.99404761904762</v>
+      </c>
+      <c r="C4" t="n">
+        <v>168</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>44802</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>20.05119047619048</v>
+      </c>
+      <c r="C5" t="n">
+        <v>168</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>44809</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>31.0125</v>
+      </c>
+      <c r="C6" t="n">
+        <v>168</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>44816</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>25.11369047619048</v>
+      </c>
+      <c r="C7" t="n">
+        <v>168</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>44823</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>14.85059523809524</v>
+      </c>
+      <c r="C8" t="n">
+        <v>168</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>44830</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>18.41488095238095</v>
+      </c>
+      <c r="C9" t="n">
+        <v>168</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>44837</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>16.20833333333333</v>
+      </c>
+      <c r="C10" t="n">
+        <v>168</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>44844</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="C11" t="n">
+        <v>168</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>44851</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>25.80595238095238</v>
+      </c>
+      <c r="C12" t="n">
+        <v>168</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>44858</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>12.21845238095238</v>
+      </c>
+      <c r="C13" t="n">
+        <v>168</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>44865</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>20.12083333333333</v>
+      </c>
+      <c r="C14" t="n">
+        <v>168</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>44872</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>22.9125</v>
+      </c>
+      <c r="C15" t="n">
+        <v>168</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>44879</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>34.61011904761905</v>
+      </c>
+      <c r="C16" t="n">
+        <v>168</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>44886</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>19.63511904761905</v>
+      </c>
+      <c r="C17" t="n">
+        <v>168</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>44893</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>14.625</v>
+      </c>
+      <c r="C18" t="n">
+        <v>168</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>44900</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>23.70238095238096</v>
+      </c>
+      <c r="C19" t="n">
+        <v>168</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>44907</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>9.691666666666666</v>
+      </c>
+      <c r="C20" t="n">
+        <v>168</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>44914</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>29.20059523809524</v>
+      </c>
+      <c r="C21" t="n">
+        <v>168</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>44921</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>27.08511904761905</v>
+      </c>
+      <c r="C22" t="n">
+        <v>168</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>44928</v>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>23.88392857142857</v>
+      </c>
+      <c r="C23" t="n">
+        <v>168</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>44935</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>17.69583333333333</v>
+      </c>
+      <c r="C24" t="n">
+        <v>168</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>44942</v>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>30.35535714285714</v>
+      </c>
+      <c r="C25" t="n">
+        <v>168</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>44949</v>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>37.675</v>
+      </c>
+      <c r="C26" t="n">
+        <v>168</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>44956</v>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>38.96369047619047</v>
+      </c>
+      <c r="C27" t="n">
+        <v>168</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>44963</v>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>37.80119047619048</v>
+      </c>
+      <c r="C28" t="n">
+        <v>168</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>44970</v>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>23.5077380952381</v>
+      </c>
+      <c r="C29" t="n">
+        <v>168</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>44977</v>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>36.42380952380952</v>
+      </c>
+      <c r="C30" t="n">
+        <v>168</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>44984</v>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>39.58333333333334</v>
+      </c>
+      <c r="C31" t="n">
+        <v>168</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>44991</v>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>22.01309523809524</v>
+      </c>
+      <c r="C32" t="n">
+        <v>168</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>44998</v>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>41.90238095238095</v>
+      </c>
+      <c r="C33" t="n">
+        <v>168</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>45005</v>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>40.27440476190476</v>
+      </c>
+      <c r="C34" t="n">
+        <v>168</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>45012</v>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>47.25595238095238</v>
+      </c>
+      <c r="C35" t="n">
+        <v>168</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>45019</v>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="C36" t="n">
+        <v>168</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>45026</v>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>17.45476190476191</v>
+      </c>
+      <c r="C37" t="n">
+        <v>168</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>45033</v>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>45.04107142857143</v>
+      </c>
+      <c r="C38" t="n">
+        <v>168</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>45040</v>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>39.31190476190476</v>
+      </c>
+      <c r="C39" t="n">
+        <v>168</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>45047</v>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>38.27559523809524</v>
+      </c>
+      <c r="C40" t="n">
+        <v>168</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>45054</v>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>38.57142857142857</v>
+      </c>
+      <c r="C41" t="n">
+        <v>168</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>45061</v>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>22.10178571428571</v>
+      </c>
+      <c r="C42" t="n">
+        <v>168</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>45068</v>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>22.7297619047619</v>
+      </c>
+      <c r="C43" t="n">
+        <v>168</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>45075</v>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>23.69285714285714</v>
+      </c>
+      <c r="C44" t="n">
+        <v>168</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>45082</v>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>17.31309523809524</v>
+      </c>
+      <c r="C45" t="n">
+        <v>168</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>45089</v>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>35.55714285714286</v>
+      </c>
+      <c r="C46" t="n">
+        <v>168</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>45096</v>
+      </c>
+      <c r="B47" s="4" t="n">
+        <v>25.45238095238096</v>
+      </c>
+      <c r="C47" t="n">
+        <v>168</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>45103</v>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>10.77559523809524</v>
+      </c>
+      <c r="C48" t="n">
+        <v>168</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>45110</v>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>19.06071428571428</v>
+      </c>
+      <c r="C49" t="n">
+        <v>168</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
+        <v>45117</v>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>17.71964285714286</v>
+      </c>
+      <c r="C50" t="n">
+        <v>168</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>45124</v>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>13.53988095238095</v>
+      </c>
+      <c r="C51" t="n">
+        <v>168</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>45131</v>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>17.13690476190476</v>
+      </c>
+      <c r="C52" t="n">
+        <v>168</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>45138</v>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>24.73392857142857</v>
+      </c>
+      <c r="C53" t="n">
+        <v>168</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>45145</v>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>19.76071428571429</v>
+      </c>
+      <c r="C54" t="n">
+        <v>168</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>45152</v>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>15.94583333333334</v>
+      </c>
+      <c r="C55" t="n">
+        <v>168</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>45159</v>
+      </c>
+      <c r="B56" s="4" t="n">
+        <v>15.38392857142857</v>
+      </c>
+      <c r="C56" t="n">
+        <v>168</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>45166</v>
+      </c>
+      <c r="B57" s="4" t="n">
+        <v>18.52380952380953</v>
+      </c>
+      <c r="C57" t="n">
+        <v>168</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>45173</v>
+      </c>
+      <c r="B58" s="4" t="n">
+        <v>14.76547619047619</v>
+      </c>
+      <c r="C58" t="n">
+        <v>168</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>45180</v>
+      </c>
+      <c r="B59" s="4" t="n">
+        <v>15.69880952380952</v>
+      </c>
+      <c r="C59" t="n">
+        <v>168</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="n">
+        <v>45187</v>
+      </c>
+      <c r="B60" s="4" t="n">
+        <v>13.65178571428571</v>
+      </c>
+      <c r="C60" t="n">
+        <v>168</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>45194</v>
+      </c>
+      <c r="B61" s="4" t="n">
+        <v>14.4797619047619</v>
+      </c>
+      <c r="C61" t="n">
+        <v>168</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n">
+        <v>45201</v>
+      </c>
+      <c r="B62" s="4" t="n">
+        <v>18.81130952380952</v>
+      </c>
+      <c r="C62" t="n">
+        <v>168</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>45208</v>
+      </c>
+      <c r="B63" s="4" t="n">
+        <v>31.60833333333333</v>
+      </c>
+      <c r="C63" t="n">
+        <v>168</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="n">
+        <v>45215</v>
+      </c>
+      <c r="B64" s="4" t="n">
+        <v>30.82916666666667</v>
+      </c>
+      <c r="C64" t="n">
+        <v>168</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>45222</v>
+      </c>
+      <c r="B65" s="4" t="n">
+        <v>23.72261904761905</v>
+      </c>
+      <c r="C65" t="n">
+        <v>168</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="n">
+        <v>45229</v>
+      </c>
+      <c r="B66" s="4" t="n">
+        <v>22.78690476190476</v>
+      </c>
+      <c r="C66" t="n">
+        <v>168</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>45236</v>
+      </c>
+      <c r="B67" s="4" t="n">
+        <v>18.32440476190476</v>
+      </c>
+      <c r="C67" t="n">
+        <v>168</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="n">
+        <v>45243</v>
+      </c>
+      <c r="B68" s="4" t="n">
+        <v>15.07797619047619</v>
+      </c>
+      <c r="C68" t="n">
+        <v>168</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>45250</v>
+      </c>
+      <c r="B69" s="4" t="n">
+        <v>16.14940476190476</v>
+      </c>
+      <c r="C69" t="n">
+        <v>168</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>45257</v>
+      </c>
+      <c r="B70" s="4" t="n">
+        <v>16.52619047619048</v>
+      </c>
+      <c r="C70" t="n">
+        <v>168</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>45264</v>
+      </c>
+      <c r="B71" s="4" t="n">
+        <v>15.91607142857143</v>
+      </c>
+      <c r="C71" t="n">
+        <v>168</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="n">
+        <v>45271</v>
+      </c>
+      <c r="B72" s="4" t="n">
+        <v>13.71547619047619</v>
+      </c>
+      <c r="C72" t="n">
+        <v>168</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="n">
+        <v>45278</v>
+      </c>
+      <c r="B73" s="4" t="n">
+        <v>13.01845238095238</v>
+      </c>
+      <c r="C73" t="n">
+        <v>168</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="n">
+        <v>45285</v>
+      </c>
+      <c r="B74" s="4" t="n">
+        <v>24.84880952380952</v>
+      </c>
+      <c r="C74" t="n">
+        <v>168</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B75" s="4" t="n">
+        <v>26.53809523809523</v>
+      </c>
+      <c r="C75" t="n">
+        <v>168</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="n">
+        <v>45299</v>
+      </c>
+      <c r="B76" s="4" t="n">
+        <v>21.725</v>
+      </c>
+      <c r="C76" t="n">
+        <v>168</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="n">
+        <v>45306</v>
+      </c>
+      <c r="B77" s="4" t="n">
+        <v>17.77738095238095</v>
+      </c>
+      <c r="C77" t="n">
+        <v>168</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="n">
+        <v>45313</v>
+      </c>
+      <c r="B78" s="4" t="n">
+        <v>29.38095238095238</v>
+      </c>
+      <c r="C78" t="n">
+        <v>168</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n">
+        <v>45320</v>
+      </c>
+      <c r="B79" s="4" t="n">
+        <v>29.74761904761905</v>
+      </c>
+      <c r="C79" t="n">
+        <v>168</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="n">
+        <v>45327</v>
+      </c>
+      <c r="B80" s="4" t="n">
+        <v>26.84404761904763</v>
+      </c>
+      <c r="C80" t="n">
+        <v>168</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="n">
+        <v>45334</v>
+      </c>
+      <c r="B81" s="4" t="n">
+        <v>32.25238095238095</v>
+      </c>
+      <c r="C81" t="n">
+        <v>168</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="n">
+        <v>45341</v>
+      </c>
+      <c r="B82" s="4" t="n">
+        <v>35.69285714285714</v>
+      </c>
+      <c r="C82" t="n">
+        <v>168</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="n">
+        <v>45348</v>
+      </c>
+      <c r="B83" s="4" t="n">
+        <v>35.5077380952381</v>
+      </c>
+      <c r="C83" t="n">
+        <v>168</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="n">
+        <v>45355</v>
+      </c>
+      <c r="B84" s="4" t="n">
+        <v>32.00714285714285</v>
+      </c>
+      <c r="C84" t="n">
+        <v>168</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="n">
+        <v>45362</v>
+      </c>
+      <c r="B85" s="4" t="n">
+        <v>26.47142857142857</v>
+      </c>
+      <c r="C85" t="n">
+        <v>168</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="n">
+        <v>45369</v>
+      </c>
+      <c r="B86" s="4" t="n">
+        <v>30.07202380952381</v>
+      </c>
+      <c r="C86" t="n">
+        <v>168</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="n">
+        <v>45376</v>
+      </c>
+      <c r="B87" s="4" t="n">
+        <v>26.92321428571429</v>
+      </c>
+      <c r="C87" t="n">
+        <v>168</v>
+      </c>
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B88" s="4" t="n">
+        <v>20.42678571428572</v>
+      </c>
+      <c r="C88" t="n">
+        <v>168</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="n">
+        <v>45390</v>
+      </c>
+      <c r="B89" s="4" t="n">
+        <v>25.17738095238096</v>
+      </c>
+      <c r="C89" t="n">
+        <v>168</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="n">
+        <v>45397</v>
+      </c>
+      <c r="B90" s="4" t="n">
+        <v>29.20238095238096</v>
+      </c>
+      <c r="C90" t="n">
+        <v>168</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="n">
+        <v>45404</v>
+      </c>
+      <c r="B91" s="4" t="n">
+        <v>29.01666666666667</v>
+      </c>
+      <c r="C91" t="n">
+        <v>168</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="n">
+        <v>45411</v>
+      </c>
+      <c r="B92" s="4" t="n">
+        <v>21.92380952380952</v>
+      </c>
+      <c r="C92" t="n">
+        <v>168</v>
+      </c>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="n">
+        <v>45418</v>
+      </c>
+      <c r="B93" s="4" t="n">
+        <v>32.23630952380952</v>
+      </c>
+      <c r="C93" t="n">
+        <v>168</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="n">
+        <v>45425</v>
+      </c>
+      <c r="B94" s="4" t="n">
+        <v>26.49345238095238</v>
+      </c>
+      <c r="C94" t="n">
+        <v>168</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="n">
+        <v>45432</v>
+      </c>
+      <c r="B95" s="4" t="n">
+        <v>24.79166666666667</v>
+      </c>
+      <c r="C95" t="n">
+        <v>168</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="n">
+        <v>45439</v>
+      </c>
+      <c r="B96" s="4" t="n">
+        <v>33.87797619047619</v>
+      </c>
+      <c r="C96" t="n">
+        <v>168</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="n">
+        <v>45446</v>
+      </c>
+      <c r="B97" s="4" t="n">
+        <v>28.43988095238095</v>
+      </c>
+      <c r="C97" t="n">
+        <v>168</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="n">
+        <v>45453</v>
+      </c>
+      <c r="B98" s="4" t="n">
+        <v>38.61369047619048</v>
+      </c>
+      <c r="C98" t="n">
+        <v>168</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="n">
+        <v>45460</v>
+      </c>
+      <c r="B99" s="4" t="n">
+        <v>23.02559523809524</v>
+      </c>
+      <c r="C99" t="n">
+        <v>168</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="n">
+        <v>45467</v>
+      </c>
+      <c r="B100" s="4" t="n">
+        <v>26.16071428571428</v>
+      </c>
+      <c r="C100" t="n">
+        <v>168</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B101" s="4" t="n">
+        <v>30.08869047619048</v>
+      </c>
+      <c r="C101" t="n">
+        <v>168</v>
+      </c>
+      <c r="D101" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="n">
+        <v>45481</v>
+      </c>
+      <c r="B102" s="4" t="n">
+        <v>21.75535714285714</v>
+      </c>
+      <c r="C102" t="n">
+        <v>168</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="n">
+        <v>45488</v>
+      </c>
+      <c r="B103" s="4" t="n">
+        <v>20.36964285714286</v>
+      </c>
+      <c r="C103" t="n">
+        <v>168</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="n">
+        <v>45495</v>
+      </c>
+      <c r="B104" s="4" t="n">
+        <v>15.76904761904762</v>
+      </c>
+      <c r="C104" t="n">
+        <v>168</v>
+      </c>
+      <c r="D104" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="n">
+        <v>45502</v>
+      </c>
+      <c r="B105" s="4" t="n">
+        <v>16.46369047619048</v>
+      </c>
+      <c r="C105" t="n">
+        <v>168</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="n">
+        <v>45509</v>
+      </c>
+      <c r="B106" s="4" t="n">
+        <v>14.50238095238095</v>
+      </c>
+      <c r="C106" t="n">
+        <v>168</v>
+      </c>
+      <c r="D106" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="n">
+        <v>45516</v>
+      </c>
+      <c r="B107" s="4" t="n">
+        <v>15.5202380952381</v>
+      </c>
+      <c r="C107" t="n">
+        <v>168</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="n">
+        <v>45523</v>
+      </c>
+      <c r="B108" s="4" t="n">
+        <v>16.08452380952381</v>
+      </c>
+      <c r="C108" t="n">
+        <v>168</v>
+      </c>
+      <c r="D108" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="n">
+        <v>45530</v>
+      </c>
+      <c r="B109" s="4" t="n">
+        <v>11.23273809523809</v>
+      </c>
+      <c r="C109" t="n">
+        <v>168</v>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="n">
+        <v>45537</v>
+      </c>
+      <c r="B110" s="4" t="n">
+        <v>13.85892857142857</v>
+      </c>
+      <c r="C110" t="n">
+        <v>168</v>
+      </c>
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="n">
+        <v>45544</v>
+      </c>
+      <c r="B111" s="4" t="n">
+        <v>15.90119047619048</v>
+      </c>
+      <c r="C111" t="n">
+        <v>168</v>
+      </c>
+      <c r="D111" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="n">
+        <v>45551</v>
+      </c>
+      <c r="B112" s="4" t="n">
+        <v>17.78869047619047</v>
+      </c>
+      <c r="C112" t="n">
+        <v>168</v>
+      </c>
+      <c r="D112" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="n">
+        <v>45558</v>
+      </c>
+      <c r="B113" s="4" t="n">
+        <v>30.71845238095237</v>
+      </c>
+      <c r="C113" t="n">
+        <v>168</v>
+      </c>
+      <c r="D113" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="n">
+        <v>45565</v>
+      </c>
+      <c r="B114" s="4" t="n">
+        <v>19.57083333333333</v>
+      </c>
+      <c r="C114" t="n">
+        <v>168</v>
+      </c>
+      <c r="D114" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="n">
+        <v>45572</v>
+      </c>
+      <c r="B115" s="4" t="n">
+        <v>16.16011904761905</v>
+      </c>
+      <c r="C115" t="n">
+        <v>168</v>
+      </c>
+      <c r="D115" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="n">
+        <v>45579</v>
+      </c>
+      <c r="B116" s="4" t="n">
+        <v>16.89583333333333</v>
+      </c>
+      <c r="C116" t="n">
+        <v>168</v>
+      </c>
+      <c r="D116" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="n">
+        <v>45586</v>
+      </c>
+      <c r="B117" s="4" t="n">
+        <v>14.3452380952381</v>
+      </c>
+      <c r="C117" t="n">
+        <v>168</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4486,7 +6717,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5503,1679 +7734,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D117"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>week_start</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>pm25</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>n_hours</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>coverage</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="n">
-        <v>44781</v>
-      </c>
-      <c r="B2" s="4" t="n">
-        <v>23.20297619047619</v>
-      </c>
-      <c r="C2" t="n">
-        <v>168</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>44788</v>
-      </c>
-      <c r="B3" s="4" t="n">
-        <v>25.58095238095238</v>
-      </c>
-      <c r="C3" t="n">
-        <v>168</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>44795</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>17.99404761904762</v>
-      </c>
-      <c r="C4" t="n">
-        <v>168</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>44802</v>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>20.05119047619048</v>
-      </c>
-      <c r="C5" t="n">
-        <v>168</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>44809</v>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>31.0125</v>
-      </c>
-      <c r="C6" t="n">
-        <v>168</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>44816</v>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>25.11369047619048</v>
-      </c>
-      <c r="C7" t="n">
-        <v>168</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>44823</v>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>14.85059523809524</v>
-      </c>
-      <c r="C8" t="n">
-        <v>168</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>44830</v>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>18.41488095238095</v>
-      </c>
-      <c r="C9" t="n">
-        <v>168</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>44837</v>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>16.20833333333333</v>
-      </c>
-      <c r="C10" t="n">
-        <v>168</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>44844</v>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>14.65</v>
-      </c>
-      <c r="C11" t="n">
-        <v>168</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>44851</v>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>25.80595238095238</v>
-      </c>
-      <c r="C12" t="n">
-        <v>168</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>44858</v>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>12.21845238095238</v>
-      </c>
-      <c r="C13" t="n">
-        <v>168</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>44865</v>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>20.12083333333333</v>
-      </c>
-      <c r="C14" t="n">
-        <v>168</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>44872</v>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>22.9125</v>
-      </c>
-      <c r="C15" t="n">
-        <v>168</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>44879</v>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>34.61011904761905</v>
-      </c>
-      <c r="C16" t="n">
-        <v>168</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>44886</v>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>19.63511904761905</v>
-      </c>
-      <c r="C17" t="n">
-        <v>168</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>44893</v>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>14.625</v>
-      </c>
-      <c r="C18" t="n">
-        <v>168</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>44900</v>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>23.70238095238096</v>
-      </c>
-      <c r="C19" t="n">
-        <v>168</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>44907</v>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>9.691666666666666</v>
-      </c>
-      <c r="C20" t="n">
-        <v>168</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>44914</v>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>29.20059523809524</v>
-      </c>
-      <c r="C21" t="n">
-        <v>168</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>44921</v>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>27.08511904761905</v>
-      </c>
-      <c r="C22" t="n">
-        <v>168</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>44928</v>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>23.88392857142857</v>
-      </c>
-      <c r="C23" t="n">
-        <v>168</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>44935</v>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>17.69583333333333</v>
-      </c>
-      <c r="C24" t="n">
-        <v>168</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>44942</v>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>30.35535714285714</v>
-      </c>
-      <c r="C25" t="n">
-        <v>168</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>44949</v>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>37.675</v>
-      </c>
-      <c r="C26" t="n">
-        <v>168</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>44956</v>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>38.96369047619047</v>
-      </c>
-      <c r="C27" t="n">
-        <v>168</v>
-      </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>44963</v>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>37.80119047619048</v>
-      </c>
-      <c r="C28" t="n">
-        <v>168</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>44970</v>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>23.5077380952381</v>
-      </c>
-      <c r="C29" t="n">
-        <v>168</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>44977</v>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>36.42380952380952</v>
-      </c>
-      <c r="C30" t="n">
-        <v>168</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>44984</v>
-      </c>
-      <c r="B31" s="4" t="n">
-        <v>39.58333333333334</v>
-      </c>
-      <c r="C31" t="n">
-        <v>168</v>
-      </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>44991</v>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>22.01309523809524</v>
-      </c>
-      <c r="C32" t="n">
-        <v>168</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>44998</v>
-      </c>
-      <c r="B33" s="4" t="n">
-        <v>41.90238095238095</v>
-      </c>
-      <c r="C33" t="n">
-        <v>168</v>
-      </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>45005</v>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>40.27440476190476</v>
-      </c>
-      <c r="C34" t="n">
-        <v>168</v>
-      </c>
-      <c r="D34" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>45012</v>
-      </c>
-      <c r="B35" s="4" t="n">
-        <v>47.25595238095238</v>
-      </c>
-      <c r="C35" t="n">
-        <v>168</v>
-      </c>
-      <c r="D35" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="n">
-        <v>45019</v>
-      </c>
-      <c r="B36" s="4" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="C36" t="n">
-        <v>168</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="n">
-        <v>45026</v>
-      </c>
-      <c r="B37" s="4" t="n">
-        <v>17.45476190476191</v>
-      </c>
-      <c r="C37" t="n">
-        <v>168</v>
-      </c>
-      <c r="D37" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="n">
-        <v>45033</v>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>45.04107142857143</v>
-      </c>
-      <c r="C38" t="n">
-        <v>168</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="n">
-        <v>45040</v>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>39.31190476190476</v>
-      </c>
-      <c r="C39" t="n">
-        <v>168</v>
-      </c>
-      <c r="D39" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="n">
-        <v>45047</v>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>38.27559523809524</v>
-      </c>
-      <c r="C40" t="n">
-        <v>168</v>
-      </c>
-      <c r="D40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>45054</v>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>38.57142857142857</v>
-      </c>
-      <c r="C41" t="n">
-        <v>168</v>
-      </c>
-      <c r="D41" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="n">
-        <v>45061</v>
-      </c>
-      <c r="B42" s="4" t="n">
-        <v>22.10178571428571</v>
-      </c>
-      <c r="C42" t="n">
-        <v>168</v>
-      </c>
-      <c r="D42" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="n">
-        <v>45068</v>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>22.7297619047619</v>
-      </c>
-      <c r="C43" t="n">
-        <v>168</v>
-      </c>
-      <c r="D43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="n">
-        <v>45075</v>
-      </c>
-      <c r="B44" s="4" t="n">
-        <v>23.69285714285714</v>
-      </c>
-      <c r="C44" t="n">
-        <v>168</v>
-      </c>
-      <c r="D44" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="n">
-        <v>45082</v>
-      </c>
-      <c r="B45" s="4" t="n">
-        <v>17.31309523809524</v>
-      </c>
-      <c r="C45" t="n">
-        <v>168</v>
-      </c>
-      <c r="D45" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="n">
-        <v>45089</v>
-      </c>
-      <c r="B46" s="4" t="n">
-        <v>35.55714285714286</v>
-      </c>
-      <c r="C46" t="n">
-        <v>168</v>
-      </c>
-      <c r="D46" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="n">
-        <v>45096</v>
-      </c>
-      <c r="B47" s="4" t="n">
-        <v>25.45238095238096</v>
-      </c>
-      <c r="C47" t="n">
-        <v>168</v>
-      </c>
-      <c r="D47" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="n">
-        <v>45103</v>
-      </c>
-      <c r="B48" s="4" t="n">
-        <v>10.77559523809524</v>
-      </c>
-      <c r="C48" t="n">
-        <v>168</v>
-      </c>
-      <c r="D48" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="n">
-        <v>45110</v>
-      </c>
-      <c r="B49" s="4" t="n">
-        <v>19.06071428571428</v>
-      </c>
-      <c r="C49" t="n">
-        <v>168</v>
-      </c>
-      <c r="D49" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="n">
-        <v>45117</v>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>17.71964285714286</v>
-      </c>
-      <c r="C50" t="n">
-        <v>168</v>
-      </c>
-      <c r="D50" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="n">
-        <v>45124</v>
-      </c>
-      <c r="B51" s="4" t="n">
-        <v>13.53988095238095</v>
-      </c>
-      <c r="C51" t="n">
-        <v>168</v>
-      </c>
-      <c r="D51" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="n">
-        <v>45131</v>
-      </c>
-      <c r="B52" s="4" t="n">
-        <v>17.13690476190476</v>
-      </c>
-      <c r="C52" t="n">
-        <v>168</v>
-      </c>
-      <c r="D52" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="n">
-        <v>45138</v>
-      </c>
-      <c r="B53" s="4" t="n">
-        <v>24.73392857142857</v>
-      </c>
-      <c r="C53" t="n">
-        <v>168</v>
-      </c>
-      <c r="D53" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="n">
-        <v>45145</v>
-      </c>
-      <c r="B54" s="4" t="n">
-        <v>19.76071428571429</v>
-      </c>
-      <c r="C54" t="n">
-        <v>168</v>
-      </c>
-      <c r="D54" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="n">
-        <v>45152</v>
-      </c>
-      <c r="B55" s="4" t="n">
-        <v>15.94583333333334</v>
-      </c>
-      <c r="C55" t="n">
-        <v>168</v>
-      </c>
-      <c r="D55" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="n">
-        <v>45159</v>
-      </c>
-      <c r="B56" s="4" t="n">
-        <v>15.38392857142857</v>
-      </c>
-      <c r="C56" t="n">
-        <v>168</v>
-      </c>
-      <c r="D56" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="n">
-        <v>45166</v>
-      </c>
-      <c r="B57" s="4" t="n">
-        <v>18.52380952380953</v>
-      </c>
-      <c r="C57" t="n">
-        <v>168</v>
-      </c>
-      <c r="D57" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="n">
-        <v>45173</v>
-      </c>
-      <c r="B58" s="4" t="n">
-        <v>14.76547619047619</v>
-      </c>
-      <c r="C58" t="n">
-        <v>168</v>
-      </c>
-      <c r="D58" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="n">
-        <v>45180</v>
-      </c>
-      <c r="B59" s="4" t="n">
-        <v>15.69880952380952</v>
-      </c>
-      <c r="C59" t="n">
-        <v>168</v>
-      </c>
-      <c r="D59" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="n">
-        <v>45187</v>
-      </c>
-      <c r="B60" s="4" t="n">
-        <v>13.65178571428571</v>
-      </c>
-      <c r="C60" t="n">
-        <v>168</v>
-      </c>
-      <c r="D60" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="n">
-        <v>45194</v>
-      </c>
-      <c r="B61" s="4" t="n">
-        <v>14.4797619047619</v>
-      </c>
-      <c r="C61" t="n">
-        <v>168</v>
-      </c>
-      <c r="D61" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="n">
-        <v>45201</v>
-      </c>
-      <c r="B62" s="4" t="n">
-        <v>18.81130952380952</v>
-      </c>
-      <c r="C62" t="n">
-        <v>168</v>
-      </c>
-      <c r="D62" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="n">
-        <v>45208</v>
-      </c>
-      <c r="B63" s="4" t="n">
-        <v>31.60833333333333</v>
-      </c>
-      <c r="C63" t="n">
-        <v>168</v>
-      </c>
-      <c r="D63" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="n">
-        <v>45215</v>
-      </c>
-      <c r="B64" s="4" t="n">
-        <v>30.82916666666667</v>
-      </c>
-      <c r="C64" t="n">
-        <v>168</v>
-      </c>
-      <c r="D64" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="n">
-        <v>45222</v>
-      </c>
-      <c r="B65" s="4" t="n">
-        <v>23.72261904761905</v>
-      </c>
-      <c r="C65" t="n">
-        <v>168</v>
-      </c>
-      <c r="D65" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="n">
-        <v>45229</v>
-      </c>
-      <c r="B66" s="4" t="n">
-        <v>22.78690476190476</v>
-      </c>
-      <c r="C66" t="n">
-        <v>168</v>
-      </c>
-      <c r="D66" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="n">
-        <v>45236</v>
-      </c>
-      <c r="B67" s="4" t="n">
-        <v>18.32440476190476</v>
-      </c>
-      <c r="C67" t="n">
-        <v>168</v>
-      </c>
-      <c r="D67" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="n">
-        <v>45243</v>
-      </c>
-      <c r="B68" s="4" t="n">
-        <v>15.07797619047619</v>
-      </c>
-      <c r="C68" t="n">
-        <v>168</v>
-      </c>
-      <c r="D68" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="n">
-        <v>45250</v>
-      </c>
-      <c r="B69" s="4" t="n">
-        <v>16.14940476190476</v>
-      </c>
-      <c r="C69" t="n">
-        <v>168</v>
-      </c>
-      <c r="D69" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="n">
-        <v>45257</v>
-      </c>
-      <c r="B70" s="4" t="n">
-        <v>16.52619047619048</v>
-      </c>
-      <c r="C70" t="n">
-        <v>168</v>
-      </c>
-      <c r="D70" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="n">
-        <v>45264</v>
-      </c>
-      <c r="B71" s="4" t="n">
-        <v>15.91607142857143</v>
-      </c>
-      <c r="C71" t="n">
-        <v>168</v>
-      </c>
-      <c r="D71" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="n">
-        <v>45271</v>
-      </c>
-      <c r="B72" s="4" t="n">
-        <v>13.71547619047619</v>
-      </c>
-      <c r="C72" t="n">
-        <v>168</v>
-      </c>
-      <c r="D72" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="n">
-        <v>45278</v>
-      </c>
-      <c r="B73" s="4" t="n">
-        <v>13.01845238095238</v>
-      </c>
-      <c r="C73" t="n">
-        <v>168</v>
-      </c>
-      <c r="D73" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="n">
-        <v>45285</v>
-      </c>
-      <c r="B74" s="4" t="n">
-        <v>24.84880952380952</v>
-      </c>
-      <c r="C74" t="n">
-        <v>168</v>
-      </c>
-      <c r="D74" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B75" s="4" t="n">
-        <v>26.53809523809523</v>
-      </c>
-      <c r="C75" t="n">
-        <v>168</v>
-      </c>
-      <c r="D75" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="n">
-        <v>45299</v>
-      </c>
-      <c r="B76" s="4" t="n">
-        <v>21.725</v>
-      </c>
-      <c r="C76" t="n">
-        <v>168</v>
-      </c>
-      <c r="D76" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="n">
-        <v>45306</v>
-      </c>
-      <c r="B77" s="4" t="n">
-        <v>17.77738095238095</v>
-      </c>
-      <c r="C77" t="n">
-        <v>168</v>
-      </c>
-      <c r="D77" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="n">
-        <v>45313</v>
-      </c>
-      <c r="B78" s="4" t="n">
-        <v>29.38095238095238</v>
-      </c>
-      <c r="C78" t="n">
-        <v>168</v>
-      </c>
-      <c r="D78" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="n">
-        <v>45320</v>
-      </c>
-      <c r="B79" s="4" t="n">
-        <v>29.74761904761905</v>
-      </c>
-      <c r="C79" t="n">
-        <v>168</v>
-      </c>
-      <c r="D79" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="n">
-        <v>45327</v>
-      </c>
-      <c r="B80" s="4" t="n">
-        <v>26.84404761904763</v>
-      </c>
-      <c r="C80" t="n">
-        <v>168</v>
-      </c>
-      <c r="D80" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="n">
-        <v>45334</v>
-      </c>
-      <c r="B81" s="4" t="n">
-        <v>32.25238095238095</v>
-      </c>
-      <c r="C81" t="n">
-        <v>168</v>
-      </c>
-      <c r="D81" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="n">
-        <v>45341</v>
-      </c>
-      <c r="B82" s="4" t="n">
-        <v>35.69285714285714</v>
-      </c>
-      <c r="C82" t="n">
-        <v>168</v>
-      </c>
-      <c r="D82" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="n">
-        <v>45348</v>
-      </c>
-      <c r="B83" s="4" t="n">
-        <v>35.5077380952381</v>
-      </c>
-      <c r="C83" t="n">
-        <v>168</v>
-      </c>
-      <c r="D83" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="n">
-        <v>45355</v>
-      </c>
-      <c r="B84" s="4" t="n">
-        <v>32.00714285714285</v>
-      </c>
-      <c r="C84" t="n">
-        <v>168</v>
-      </c>
-      <c r="D84" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="n">
-        <v>45362</v>
-      </c>
-      <c r="B85" s="4" t="n">
-        <v>26.47142857142857</v>
-      </c>
-      <c r="C85" t="n">
-        <v>168</v>
-      </c>
-      <c r="D85" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="n">
-        <v>45369</v>
-      </c>
-      <c r="B86" s="4" t="n">
-        <v>30.07202380952381</v>
-      </c>
-      <c r="C86" t="n">
-        <v>168</v>
-      </c>
-      <c r="D86" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="n">
-        <v>45376</v>
-      </c>
-      <c r="B87" s="4" t="n">
-        <v>26.92321428571429</v>
-      </c>
-      <c r="C87" t="n">
-        <v>168</v>
-      </c>
-      <c r="D87" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B88" s="4" t="n">
-        <v>20.42678571428572</v>
-      </c>
-      <c r="C88" t="n">
-        <v>168</v>
-      </c>
-      <c r="D88" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="n">
-        <v>45390</v>
-      </c>
-      <c r="B89" s="4" t="n">
-        <v>25.17738095238096</v>
-      </c>
-      <c r="C89" t="n">
-        <v>168</v>
-      </c>
-      <c r="D89" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="n">
-        <v>45397</v>
-      </c>
-      <c r="B90" s="4" t="n">
-        <v>29.20238095238096</v>
-      </c>
-      <c r="C90" t="n">
-        <v>168</v>
-      </c>
-      <c r="D90" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="n">
-        <v>45404</v>
-      </c>
-      <c r="B91" s="4" t="n">
-        <v>29.01666666666667</v>
-      </c>
-      <c r="C91" t="n">
-        <v>168</v>
-      </c>
-      <c r="D91" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="n">
-        <v>45411</v>
-      </c>
-      <c r="B92" s="4" t="n">
-        <v>21.92380952380952</v>
-      </c>
-      <c r="C92" t="n">
-        <v>168</v>
-      </c>
-      <c r="D92" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="n">
-        <v>45418</v>
-      </c>
-      <c r="B93" s="4" t="n">
-        <v>32.23630952380952</v>
-      </c>
-      <c r="C93" t="n">
-        <v>168</v>
-      </c>
-      <c r="D93" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="n">
-        <v>45425</v>
-      </c>
-      <c r="B94" s="4" t="n">
-        <v>26.49345238095238</v>
-      </c>
-      <c r="C94" t="n">
-        <v>168</v>
-      </c>
-      <c r="D94" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="n">
-        <v>45432</v>
-      </c>
-      <c r="B95" s="4" t="n">
-        <v>24.79166666666667</v>
-      </c>
-      <c r="C95" t="n">
-        <v>168</v>
-      </c>
-      <c r="D95" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="n">
-        <v>45439</v>
-      </c>
-      <c r="B96" s="4" t="n">
-        <v>33.87797619047619</v>
-      </c>
-      <c r="C96" t="n">
-        <v>168</v>
-      </c>
-      <c r="D96" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="n">
-        <v>45446</v>
-      </c>
-      <c r="B97" s="4" t="n">
-        <v>28.43988095238095</v>
-      </c>
-      <c r="C97" t="n">
-        <v>168</v>
-      </c>
-      <c r="D97" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="n">
-        <v>45453</v>
-      </c>
-      <c r="B98" s="4" t="n">
-        <v>38.61369047619048</v>
-      </c>
-      <c r="C98" t="n">
-        <v>168</v>
-      </c>
-      <c r="D98" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="n">
-        <v>45460</v>
-      </c>
-      <c r="B99" s="4" t="n">
-        <v>23.02559523809524</v>
-      </c>
-      <c r="C99" t="n">
-        <v>168</v>
-      </c>
-      <c r="D99" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="n">
-        <v>45467</v>
-      </c>
-      <c r="B100" s="4" t="n">
-        <v>26.16071428571428</v>
-      </c>
-      <c r="C100" t="n">
-        <v>168</v>
-      </c>
-      <c r="D100" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="n">
-        <v>45474</v>
-      </c>
-      <c r="B101" s="4" t="n">
-        <v>30.08869047619048</v>
-      </c>
-      <c r="C101" t="n">
-        <v>168</v>
-      </c>
-      <c r="D101" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="n">
-        <v>45481</v>
-      </c>
-      <c r="B102" s="4" t="n">
-        <v>21.75535714285714</v>
-      </c>
-      <c r="C102" t="n">
-        <v>168</v>
-      </c>
-      <c r="D102" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="n">
-        <v>45488</v>
-      </c>
-      <c r="B103" s="4" t="n">
-        <v>20.36964285714286</v>
-      </c>
-      <c r="C103" t="n">
-        <v>168</v>
-      </c>
-      <c r="D103" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="n">
-        <v>45495</v>
-      </c>
-      <c r="B104" s="4" t="n">
-        <v>15.76904761904762</v>
-      </c>
-      <c r="C104" t="n">
-        <v>168</v>
-      </c>
-      <c r="D104" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="3" t="n">
-        <v>45502</v>
-      </c>
-      <c r="B105" s="4" t="n">
-        <v>16.46369047619048</v>
-      </c>
-      <c r="C105" t="n">
-        <v>168</v>
-      </c>
-      <c r="D105" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="3" t="n">
-        <v>45509</v>
-      </c>
-      <c r="B106" s="4" t="n">
-        <v>14.50238095238095</v>
-      </c>
-      <c r="C106" t="n">
-        <v>168</v>
-      </c>
-      <c r="D106" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="n">
-        <v>45516</v>
-      </c>
-      <c r="B107" s="4" t="n">
-        <v>15.5202380952381</v>
-      </c>
-      <c r="C107" t="n">
-        <v>168</v>
-      </c>
-      <c r="D107" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="n">
-        <v>45523</v>
-      </c>
-      <c r="B108" s="4" t="n">
-        <v>16.08452380952381</v>
-      </c>
-      <c r="C108" t="n">
-        <v>168</v>
-      </c>
-      <c r="D108" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="3" t="n">
-        <v>45530</v>
-      </c>
-      <c r="B109" s="4" t="n">
-        <v>11.23273809523809</v>
-      </c>
-      <c r="C109" t="n">
-        <v>168</v>
-      </c>
-      <c r="D109" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="3" t="n">
-        <v>45537</v>
-      </c>
-      <c r="B110" s="4" t="n">
-        <v>13.85892857142857</v>
-      </c>
-      <c r="C110" t="n">
-        <v>168</v>
-      </c>
-      <c r="D110" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="3" t="n">
-        <v>45544</v>
-      </c>
-      <c r="B111" s="4" t="n">
-        <v>15.90119047619048</v>
-      </c>
-      <c r="C111" t="n">
-        <v>168</v>
-      </c>
-      <c r="D111" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="3" t="n">
-        <v>45551</v>
-      </c>
-      <c r="B112" s="4" t="n">
-        <v>17.78869047619047</v>
-      </c>
-      <c r="C112" t="n">
-        <v>168</v>
-      </c>
-      <c r="D112" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="3" t="n">
-        <v>45558</v>
-      </c>
-      <c r="B113" s="4" t="n">
-        <v>30.71845238095237</v>
-      </c>
-      <c r="C113" t="n">
-        <v>168</v>
-      </c>
-      <c r="D113" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="3" t="n">
-        <v>45565</v>
-      </c>
-      <c r="B114" s="4" t="n">
-        <v>19.57083333333333</v>
-      </c>
-      <c r="C114" t="n">
-        <v>168</v>
-      </c>
-      <c r="D114" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="n">
-        <v>45572</v>
-      </c>
-      <c r="B115" s="4" t="n">
-        <v>16.16011904761905</v>
-      </c>
-      <c r="C115" t="n">
-        <v>168</v>
-      </c>
-      <c r="D115" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="3" t="n">
-        <v>45579</v>
-      </c>
-      <c r="B116" s="4" t="n">
-        <v>16.89583333333333</v>
-      </c>
-      <c r="C116" t="n">
-        <v>168</v>
-      </c>
-      <c r="D116" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="3" t="n">
-        <v>45586</v>
-      </c>
-      <c r="B117" s="4" t="n">
-        <v>14.3452380952381</v>
-      </c>
-      <c r="C117" t="n">
-        <v>168</v>
-      </c>
-      <c r="D117" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -7241,6 +7806,27 @@
       <c r="A9" t="inlineStr">
         <is>
           <t>Akar_Model memuat modulus akar AR/MA; nilai &gt; 1 menunjukkan stasioneritas/invertibilitas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Kandidat_MA memuat model MA(q) galat, terpisah dari MA(3)/MA(8) yang merupakan penghalus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Diagnostik_Model memuat Ljung-Box, Jarque-Bera, dan ARCH untuk model final tiap keluarga.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Pemeriksaan pencilan memakai batas IQR 1,5 dan |z| &gt; 3; tidak ditemukan pencilan.</t>
         </is>
       </c>
     </row>
@@ -7663,23 +8249,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="43" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7695,60 +8282,65 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>k</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>AIC</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>AICc</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>BIC</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>MAE</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>RMSE</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>MAPE</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>sMAPE</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>MASE</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>LB20_p</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Konvergen</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>AIC_sebanding</t>
         </is>
@@ -7765,30 +8357,30 @@
           <t>ŷₜ₊ₕ = yₜ</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4" t="n">
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4" t="n">
         <v>2.768601190476189</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="I2" s="4" t="n">
         <v>4.643271123307041</v>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="J2" s="4" t="n">
         <v>14.98289196152293</v>
       </c>
-      <c r="J2" s="4" t="n">
+      <c r="K2" s="4" t="n">
         <v>15.24476612788105</v>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="L2" s="4" t="n">
         <v>0.3568640990570282</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Benchmark</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Tidak</t>
         </is>
@@ -7805,30 +8397,30 @@
           <t>Rata-rata bergerak 3 minggu</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="4" t="n">
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4" t="n">
         <v>2.940688253262326</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="I3" s="4" t="n">
         <v>4.660454951373567</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="J3" s="4" t="n">
         <v>16.46290457917413</v>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="K3" s="4" t="n">
         <v>16.26986005518134</v>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>0.3790455872510654</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Smoothing</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Tidak</t>
         </is>
@@ -7846,41 +8438,44 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
         <v>4</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="E4" s="4" t="n">
         <v>309.7221716978905</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="F4" s="4" t="n">
         <v>310.6312626069815</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="G4" s="4" t="n">
         <v>317.2894528903331</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="H4" s="4" t="n">
         <v>2.950629908002577</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="I4" s="4" t="n">
         <v>4.813991610955503</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="J4" s="4" t="n">
         <v>15.9546166422047</v>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="K4" s="4" t="n">
         <v>16.27696797944449</v>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="L4" s="4" t="n">
         <v>0.3803270356858273</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="M4" s="4" t="n">
         <v>0.08110861057741714</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -7898,41 +8493,44 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
         <v>7</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="E5" s="4" t="n">
         <v>684.3808324622838</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="F5" s="4" t="n">
         <v>685.5851335375527</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>702.6866760801727</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>4.125216607555156</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="I5" s="4" t="n">
         <v>5.075720613510741</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="J5" s="4" t="n">
         <v>25.3237131201096</v>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="K5" s="4" t="n">
         <v>22.82442522025734</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="L5" s="4" t="n">
         <v>0.531727615062196</v>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="M5" s="4" t="n">
         <v>0.5335656739696019</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Bonus</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -7949,39 +8547,39 @@
           <t>Trend aditif</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>10</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="E6" s="4" t="n">
         <v>421.4811600096669</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="F6" s="4" t="n">
         <v>423.8467514075164</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>4.543960771052463</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="I6" s="4" t="n">
         <v>5.357598885963195</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="J6" s="4" t="n">
         <v>28.37371683921007</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="K6" s="4" t="n">
         <v>24.96725768965563</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="L6" s="4" t="n">
         <v>0.5857024378557069</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="M6" s="4" t="n">
         <v>0.5344432758569706</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Smoothing</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Tidak</t>
         </is>
@@ -7998,39 +8596,39 @@
           <t>Simple exponential smoothing</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="E7" s="4" t="n">
         <v>417.4955616803405</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="F7" s="4" t="n">
         <v>419.86115307819</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>4.731918908534044</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="I7" s="4" t="n">
         <v>5.46432464231268</v>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="J7" s="4" t="n">
         <v>29.67573094550699</v>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="K7" s="4" t="n">
         <v>25.91083558582066</v>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="L7" s="4" t="n">
         <v>0.6099296583104032</v>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="M7" s="4" t="n">
         <v>0.5340752650595835</v>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Smoothing</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Tidak</t>
         </is>
@@ -8048,41 +8646,44 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="E8" s="4" t="n">
         <v>679.6219083278886</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="F8" s="4" t="n">
         <v>680.2670696182112</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>692.5975075785616</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>5.085209742430336</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="I8" s="4" t="n">
         <v>5.708349194075499</v>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="J8" s="4" t="n">
         <v>32.14916097419575</v>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="K8" s="4" t="n">
         <v>27.63055514092916</v>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="L8" s="4" t="n">
         <v>0.6554677501010167</v>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="M8" s="4" t="n">
         <v>0.8711266890833191</v>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -8100,41 +8701,44 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
         <v>14</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="E9" s="4" t="n">
         <v>641.6098183791074</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="F9" s="4" t="n">
         <v>646.3289195027029</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>676.914858457794</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>6.187101578648595</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="I9" s="4" t="n">
         <v>6.572378197518031</v>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="J9" s="4" t="n">
         <v>39.46862531014892</v>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="K9" s="4" t="n">
         <v>32.37835886739305</v>
       </c>
-      <c r="K9" s="4" t="n">
+      <c r="L9" s="4" t="n">
         <v>0.797498187255705</v>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="M9" s="4" t="n">
         <v>0.9935984804513631</v>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -8151,30 +8755,30 @@
           <t>Rata-rata bergerak 8 minggu</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="4" t="n">
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="n">
         <v>6.161828340640381</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="I10" s="4" t="n">
         <v>6.687015466377627</v>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="J10" s="4" t="n">
         <v>39.45800131754925</v>
       </c>
-      <c r="J10" s="4" t="n">
+      <c r="K10" s="4" t="n">
         <v>32.55279327162682</v>
       </c>
-      <c r="K10" s="4" t="n">
+      <c r="L10" s="4" t="n">
         <v>0.7942405453305766</v>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Smoothing</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Tidak</t>
         </is>
@@ -8191,39 +8795,39 @@
           <t>Trend + musiman aditif, s=52</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>10</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="E11" s="4" t="n">
         <v>428.4415904377905</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="F11" s="4" t="n">
         <v>430.8071818356399</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>5.186213299157383</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="I11" s="4" t="n">
         <v>6.73856193619728</v>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="J11" s="4" t="n">
         <v>28.74309885120082</v>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="K11" s="4" t="n">
         <v>29.26230120586158</v>
       </c>
-      <c r="K11" s="4" t="n">
+      <c r="L11" s="4" t="n">
         <v>0.668486795024115</v>
       </c>
-      <c r="L11" s="4" t="n">
+      <c r="M11" s="4" t="n">
         <v>0.005944823224896603</v>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Smoothing</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Tidak</t>
         </is>
@@ -8241,41 +8845,44 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
         <v>7</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="E12" s="4" t="n">
         <v>686.8343778394806</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="F12" s="4" t="n">
         <v>688.0517691438284</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>705.0705691413972</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>6.795395897860953</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="I12" s="4" t="n">
         <v>7.067464405708389</v>
       </c>
-      <c r="I12" s="4" t="n">
+      <c r="J12" s="4" t="n">
         <v>43.74325119904389</v>
       </c>
-      <c r="J12" s="4" t="n">
+      <c r="K12" s="4" t="n">
         <v>35.3696482006636</v>
       </c>
-      <c r="K12" s="4" t="n">
+      <c r="L12" s="4" t="n">
         <v>0.8759054367122038</v>
       </c>
-      <c r="L12" s="4" t="n">
+      <c r="M12" s="4" t="n">
         <v>0.8634189972435953</v>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -8292,30 +8899,30 @@
           <t>ŷₜ₊ₕ = yₜ₊ₕ₋₅₂</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4" t="n">
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4" t="n">
         <v>6.223214285714286</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="I13" s="4" t="n">
         <v>8.585117187026912</v>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="J13" s="4" t="n">
         <v>36.62576623436386</v>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="K13" s="4" t="n">
         <v>30.74472467712764</v>
       </c>
-      <c r="K13" s="4" t="n">
+      <c r="L13" s="4" t="n">
         <v>0.8021530030940567</v>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Benchmark</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Tidak</t>
         </is>
